--- a/Monitor/TFL_ICStock.xlsx
+++ b/Monitor/TFL_ICStock.xlsx
@@ -3,14 +3,18 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4620" yWindow="3800" windowWidth="25080" windowHeight="12260" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1140" yWindow="760" windowWidth="29100" windowHeight="17940" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ppn0" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ppn" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ppn" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ppn0" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ppnOLD" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="price" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="zhengnengliang_price" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="zhengnengliang_price_sum" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ppn'!$B$1:$B$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ppnOLD'!$B$1:$B$62</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,8 +22,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
+  </numFmts>
+  <fonts count="12">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -64,11 +70,54 @@
       <name val="宋体"/>
       <charset val="134"/>
       <family val="3"/>
+      <color rgb="FF000000"/>
+      <sz val="14"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color rgb="FF000000"/>
       <sz val="9"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="PingFang SC"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <color rgb="FF333333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color rgb="FF000000"/>
+      <sz val="14"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -81,8 +130,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -129,12 +184,87 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -166,6 +296,53 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -532,6 +709,845 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B71"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <cols>
+    <col width="28.83203125" customWidth="1" style="11" min="1" max="1"/>
+    <col width="10.83203125" customWidth="1" style="11" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>11AA02E48T-I/TT</t>
+        </is>
+      </c>
+      <c r="B1" s="25" t="inlineStr">
+        <is>
+          <t>MICROCHIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>14212R-500</t>
+        </is>
+      </c>
+      <c r="B2" s="25" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="17" customHeight="1">
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>14222R-800</t>
+        </is>
+      </c>
+      <c r="B3" s="25" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17" customHeight="1">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>14235R-2000</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>14255R-100</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>15311R-1000</t>
+        </is>
+      </c>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>5-1879071-9</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>50020R-10</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>55010R-10</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>55040R-10</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>5P49V6901A000NLGI</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>72V211L15PFGI</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>8N3QV01FG-0055CDI8</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>APA150-PQG208I</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>MICROCHIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>AT25DF641A-MH-Y</t>
+        </is>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>AT45DB641E-SHN-T</t>
+        </is>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>ATMEGA168-15AD</t>
+        </is>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>MICROCHIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>CLA4603-085LF</t>
+        </is>
+      </c>
+      <c r="B18" s="25" t="inlineStr">
+        <is>
+          <t>Skyworks</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>CLA4605-000</t>
+        </is>
+      </c>
+      <c r="B19" s="25" t="inlineStr">
+        <is>
+          <t>Skyworks</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>CLA4605-085LF</t>
+        </is>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>Skyworks</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>CLA4606-085LF</t>
+        </is>
+      </c>
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>Skyworks</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>CLA4610-085LF</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>Skyworks</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="27" t="inlineStr">
+        <is>
+          <t>CY62177EV18LL-70BAXI</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="27" t="inlineStr">
+        <is>
+          <t>CY7C2665KV18-450BZXI</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>CY7C68013A-56PVXC</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>CY7C68014A-56LTXC</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>FS3000-1015</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>HS3002</t>
+        </is>
+      </c>
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>HS3101</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>HS4011</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>IPB072N15N3GATMA1</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>IPF016N06NF2S</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>IPL60R125P7</t>
+        </is>
+      </c>
+      <c r="B33" s="25" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>IPT034N15NM6</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>IR2153STRPBF</t>
+        </is>
+      </c>
+      <c r="B35" s="25" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>IRF5210PBF</t>
+        </is>
+      </c>
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>IRF5305PBF</t>
+        </is>
+      </c>
+      <c r="B37" s="25" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>IRPS5401MTRPBF</t>
+        </is>
+      </c>
+      <c r="B38" s="25" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>IRS2004STRPBF</t>
+        </is>
+      </c>
+      <c r="B39" s="25" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>MIMX8ML8CVNKZAB</t>
+        </is>
+      </c>
+      <c r="B40" s="25" t="inlineStr">
+        <is>
+          <t>NXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="25" t="inlineStr">
+        <is>
+          <t>MPXM2202AS</t>
+        </is>
+      </c>
+      <c r="B41" s="25" t="inlineStr">
+        <is>
+          <t>NXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="25" t="inlineStr">
+        <is>
+          <t>MRF101AN</t>
+        </is>
+      </c>
+      <c r="B42" s="25" t="inlineStr">
+        <is>
+          <t>NXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>MRF300AN</t>
+        </is>
+      </c>
+      <c r="B43" s="25" t="inlineStr">
+        <is>
+          <t>NXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="25" t="inlineStr">
+        <is>
+          <t>MRF300BN</t>
+        </is>
+      </c>
+      <c r="B44" s="25" t="inlineStr">
+        <is>
+          <t>NXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="25" t="inlineStr">
+        <is>
+          <t>MT29F512G08CMCEBJ4-37ITR:E</t>
+        </is>
+      </c>
+      <c r="B45" s="25" t="inlineStr">
+        <is>
+          <t>MICRON</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="25" t="inlineStr">
+        <is>
+          <t>MVF60NN152CMK50</t>
+        </is>
+      </c>
+      <c r="B46" s="25" t="inlineStr">
+        <is>
+          <t>NXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="25" t="inlineStr">
+        <is>
+          <t>MVTM36BF240M005A00</t>
+        </is>
+      </c>
+      <c r="B47" s="25" t="inlineStr">
+        <is>
+          <t>VICOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="25" t="inlineStr">
+        <is>
+          <t>MW6S004NT1</t>
+        </is>
+      </c>
+      <c r="B48" s="25" t="inlineStr">
+        <is>
+          <t>NXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="25" t="inlineStr">
+        <is>
+          <t>PI3301-00-LGIZ</t>
+        </is>
+      </c>
+      <c r="B49" s="25" t="inlineStr">
+        <is>
+          <t>VICOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="25" t="inlineStr">
+        <is>
+          <t>PI3302-00-LGIZ</t>
+        </is>
+      </c>
+      <c r="B50" s="25" t="inlineStr">
+        <is>
+          <t>VICOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="25" t="inlineStr">
+        <is>
+          <t>PVG612AS-TPBF</t>
+        </is>
+      </c>
+      <c r="B51" s="25" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="25" t="inlineStr">
+        <is>
+          <t>R5F5651EHDBG#20</t>
+        </is>
+      </c>
+      <c r="B52" s="25" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="25" t="inlineStr">
+        <is>
+          <t>R7FA4M1AB3CNB#BA0</t>
+        </is>
+      </c>
+      <c r="B53" s="25" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="25" t="inlineStr">
+        <is>
+          <t>S29GL032N90BFI032</t>
+        </is>
+      </c>
+      <c r="B54" s="25" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="27" t="inlineStr">
+        <is>
+          <t>SLB 9665TT2.0 FW5.63</t>
+        </is>
+      </c>
+      <c r="B55" s="25" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="25" t="inlineStr">
+        <is>
+          <t>SLB 9672VU2.0 FW15.23</t>
+        </is>
+      </c>
+      <c r="B56" s="25" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="27" t="inlineStr">
+        <is>
+          <t>SLB9665TT20FW563XUMA3</t>
+        </is>
+      </c>
+      <c r="B57" s="25" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="25" t="inlineStr">
+        <is>
+          <t>SLB9672VU20FW1523XTMA1</t>
+        </is>
+      </c>
+      <c r="B58" s="25" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="25" t="inlineStr">
+        <is>
+          <t>SMP1330-005LF</t>
+        </is>
+      </c>
+      <c r="B59" s="25" t="inlineStr">
+        <is>
+          <t>Skyworks</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="25" t="inlineStr">
+        <is>
+          <t>SMS7621-040LF</t>
+        </is>
+      </c>
+      <c r="B60" s="25" t="inlineStr">
+        <is>
+          <t>Skyworks</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="25" t="inlineStr">
+        <is>
+          <t>THS5010KJ</t>
+        </is>
+      </c>
+      <c r="B61" s="25" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="25" t="inlineStr">
+        <is>
+          <t>TPS79133DBVR</t>
+        </is>
+      </c>
+      <c r="B62" s="25" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="25" t="inlineStr">
+        <is>
+          <t>V24C8M100BL</t>
+        </is>
+      </c>
+      <c r="B63" s="25" t="inlineStr">
+        <is>
+          <t>VICOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="25" t="inlineStr">
+        <is>
+          <t>V300B5T200BL</t>
+        </is>
+      </c>
+      <c r="B64" s="25" t="inlineStr">
+        <is>
+          <t>VICOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="25" t="inlineStr">
+        <is>
+          <t>ZMOD4410AI2R</t>
+        </is>
+      </c>
+      <c r="B65" s="25" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="25" t="inlineStr">
+        <is>
+          <t>ZMOD4410AI4R</t>
+        </is>
+      </c>
+      <c r="B66" s="25" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="25" t="inlineStr">
+        <is>
+          <t>ZMOD4510AI4R</t>
+        </is>
+      </c>
+      <c r="B67" s="25" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="28" t="n"/>
+      <c r="B68" s="28" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="28" t="n"/>
+      <c r="B69" s="28" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="28" t="n"/>
+      <c r="B70" s="28" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="28" t="n"/>
+      <c r="B71" s="28" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
@@ -896,7 +1912,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -921,117 +1937,117 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>5P49V6901A000NLGI</t>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>AD5260BRUZ200-RL7</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>RENESAS</t>
+          <t>ADI</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>7007L20PFGI</t>
+          <t>ADSP-21489KSWZ-4B</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>RENESAS</t>
+          <t>ADI</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>AD5260BRUZ200-RL7</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>CY7C68013A-56PVXC</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>INFINEON</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>ADSP-21489KSWZ-4B</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>CY7C68014A-56LTXC</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>INFINEON</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>APA150-FGG144I</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ETT580N16P60</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>MICROCHIP</t>
+          <t>INFINEON</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>APA150-PQG208I</t>
+          <t>FF1200R17KP4_B2</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>MICROCHIP</t>
+          <t>INFINEON</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>ATMEGA168-15AD</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>FF1400R12IP4</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>MICROCHIP</t>
+          <t>INFINEON</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>BCM48BF060T240A00</t>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>FF450R12ME4</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>VICOR</t>
+          <t>INFINEON</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>BCM48BF080T240A00</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>FF600R12ME4B72</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>VICOR</t>
+          <t>INFINEON</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>CY7C68013A-56PVXC</t>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>FF600R17ME4</t>
         </is>
       </c>
       <c r="B11" s="1" t="inlineStr">
@@ -1041,9 +2057,9 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>CY7C68014A-56LTXC</t>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>FF750R17ME7D_B11</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
@@ -1053,21 +2069,21 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>DSPIC30F6014A-30I/PF</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>IR2110STRPBF</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>MICROCHIP</t>
+          <t>INFINEON</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>ETT580N16P60</t>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>IRF540NPBF</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
@@ -1079,7 +2095,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>FF1200R17KP4_B2</t>
+          <t>IRFZ44NPBF</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
@@ -1089,9 +2105,9 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>FF1400R12IP4</t>
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>IRPS5401MTRPBF</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
@@ -1103,7 +2119,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>FF450R12ME4</t>
+          <t>IRS2004STRPBF</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
@@ -1113,21 +2129,21 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>FF600R12ME4B72</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>IRS2113STRPBF</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>INFINEON</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>FF600R17ME4</t>
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>IRF640NPBF</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
@@ -1137,9 +2153,9 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>FF750R17ME7D_B11</t>
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>IRLR8726TRPBF</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
@@ -1151,19 +2167,19 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>HFW4A1201K00</t>
+          <t>PVG612AS-TPBF</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>INFINEON</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>IR2110STRPBF</t>
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>PVG612ASPBF</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
@@ -1175,7 +2191,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>IRF540NPBF</t>
+          <t>PVT412ASPBF</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
@@ -1185,21 +2201,21 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>MD82C52/B</t>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>S29GL032N90BFI032</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>RENESAS</t>
+          <t>INFINEON</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>IRFZ44NPBF</t>
+          <t>SLB9665TT2.0FW5.63</t>
         </is>
       </c>
       <c r="B25" s="1" t="inlineStr">
@@ -1209,21 +2225,21 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>MRF101AN</t>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>SLB9665TT20FW563XUMA3</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>NXP</t>
+          <t>INFINEON</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>IRPS5401MTRPBF</t>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>TT320N16SO</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
@@ -1233,9 +2249,9 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>IRS2004STRPBF</t>
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>TT320N16SOFHPSA1</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
@@ -1245,98 +2261,98 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>IRS2113STRPBF</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>INFINEON</t>
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>APA150-FGG144I</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>MICROCHIP</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>LMD18200-2D/883</t>
+          <t>APA150-PQG208I</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>MICROCHIP</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>M391A2G43BB2-CWEQY</t>
+          <t>ATMEGA168-15AD</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>SAMSUNG</t>
+          <t>MICROCHIP</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>M41T94MH6F</t>
+          <t>DSPIC30F6014A-30I/PF</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>MICROCHIP</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>MD82C52/7</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Renesas</t>
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>MT29F2G08ABAEAWP-IT:E</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>MICRON</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>IRF640NPBF</t>
+          <t>MT29F512G08CMCEBJ4-37ITR:E</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>INFINEON</t>
+          <t>MICRON</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
+          <t>MRF101AN</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>NXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
           <t>MPXM2202AS</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
+      <c r="B36" s="1" t="inlineStr">
         <is>
           <t>NXP</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>IRLR8726TRPBF</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>INFINEON</t>
         </is>
       </c>
     </row>
@@ -1379,240 +2395,240 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>MT29F2G08ABAEAWP-IT:E</t>
+          <t>MVF60NN152CMK50</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>MICRON</t>
+          <t>NXP</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>MT29F512G08CMCEBJ4-37ITR:E</t>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>MW6S004NT1</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>Micron</t>
+          <t>NXP</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>MVF60NN152CMK50</t>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>5P49V6901A000NLGI</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>NXP</t>
+          <t>RENESAS</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>MVTM36BF240M005A00</t>
+          <t>7007L20PFGI</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>VICOR</t>
+          <t>RENESAS</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>MW6S004NT1</t>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>MD82C52/B</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>NXP</t>
+          <t>RENESAS</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>PI3301-00-LGIZ</t>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>MD82C52/7</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>VICOR</t>
+          <t>RENESAS</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>PI3302-00-LGIZ</t>
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>M391A2G43BB2-CWEQY</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>VICOR</t>
+          <t>SAMSUNG</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>PI3740-00-LGIZ</t>
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>M41T94MH6F</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>VICOR</t>
+          <t>ST</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>PVG612AS-TPBF</t>
+          <t>HFW4A1201K00</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>INFINEON</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>PVG612ASPBF</t>
+          <t>LMD18200-2D/883</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>INFINEON</t>
+          <t>TI</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>PVT412ASPBF</t>
+          <t>TMS320C54CSTPGE</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>INFINEON</t>
+          <t>TI</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>QPI-5LZ</t>
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>TMS320C6745DPTPD4</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>VICOR</t>
+          <t>TI</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>S29GL032N90BFI032</t>
+          <t>TPS22810DRVR</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>INFINEON</t>
+          <t>TI</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>SLB9665TT2.0FW5.63</t>
+          <t>BCM48BF060T240A00</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>INFINEON</t>
+          <t>VICOR</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>SLB9665TT20FW563XUMA3</t>
+          <t>BCM48BF080T240A00</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>INFINEON</t>
+          <t>VICOR</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>TMS320C54CSTPGE</t>
+          <t>MVTM36BF240M005A00</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>VICOR</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>TMS320C6745DPTPD4</t>
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>PI3301-00-LGIZ</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>VICOR</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>TPS22810DRVR</t>
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>PI3302-00-LGIZ</t>
         </is>
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>VICOR</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TT320N16SO</t>
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>PI3740-00-LGIZ</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>INFINEON</t>
+          <t>VICOR</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>TT320N16SOFHPSA1</t>
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>QPI-5LZ</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>INFINEON</t>
+          <t>VICOR</t>
         </is>
       </c>
     </row>
@@ -1657,4 +2673,4107 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B90"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>IR2110STRPBF</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>TPS22810DRVR</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>MT29F2G08ABAEAWP-IT:E</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>MICRON</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ADSP-21489KSWZ-4B</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>ADI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>IRF640NPBF</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>IRF540NPBF</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>DSPIC30F6014A-30I/PF</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>MICROCHIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>IRLR8726TRPBF</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>IRFZ44NPBF</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>IRPS5401MTRPBF</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>CY7C68013A-56PVXC</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>Infineon</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>FF450R12ME4</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Infineon</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>IRS2004STRPBF</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>FF1400R12IP4</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Infineon</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>4202-004</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>CTS (TUSONIX)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>4601-053</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>CTS (TUSONIX)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>CM1800HG-66X</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>Mitsubishi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>RM1200DG-66X</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>Mitsubishi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>TPS22810DRVR</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>11AA02E48T-I/TT</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>MICROCHIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>LTM4668AIY#PBF</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>ADI</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>14212R-500</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>14222R-800</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>14235R-2000</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>14255R-100</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>15311R-1000</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>50020R-10</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>5-1879071-9</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>55010R-10</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>55040R-10</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>5P49V6901A000NLGI</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>72V211L15PFGI</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>8N3QV01FG-0055CDI8</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>APA150-PQG208I</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>MICROCHIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>AT25DF641A-MH-Y</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>AT45DB641E-SHN-T</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>ATMEGA168-15AD</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>MICROCHIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>CLA4603-085LF</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>Skyworks</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>CLA4605-000</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>Skyworks</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>CLA4605-085LF</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>Skyworks</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>CLA4606-085LF</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>Skyworks</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>CLA4610-085LF</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>Skyworks</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>CY62177EV18LL-70BAXI</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="17" t="inlineStr">
+        <is>
+          <t>CY7C2665KV18-450BZXI</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>CY7C68013A-56PVXC</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>CY7C68014A-56LTXC</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>DSPIC30F6014A-30I/PF</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>MICROCHIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="17" t="inlineStr">
+        <is>
+          <t>FM25V02A-GTR</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>FS3000-1015</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>HS3002</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>HS3101</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>HS4011</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>IPB072N15N3GATMA1</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>IPF016N06NF2S</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>IPL60R125P7</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>IPT034N15NM6</t>
+        </is>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="13" t="inlineStr">
+        <is>
+          <t>IR2153STRPBF</t>
+        </is>
+      </c>
+      <c r="B57" s="13" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>IRF5210PBF</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>IRF5305PBF</t>
+        </is>
+      </c>
+      <c r="B59" s="13" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>IRPS5401MTRPBF</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="13" t="inlineStr">
+        <is>
+          <t>IRS2004STRPBF</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>M41T94MH6F</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>STM</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="13" t="inlineStr">
+        <is>
+          <t>MIMX8ML8CVNKZAB</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>NXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>MPXM2202AS</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>NXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>MRF101AN</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>NXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>MRF300AN</t>
+        </is>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>NXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="13" t="inlineStr">
+        <is>
+          <t>MRF300BN</t>
+        </is>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>NXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>MT29F512G08CMCEBJ4-37ITR:E</t>
+        </is>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>MICRON</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="13" t="inlineStr">
+        <is>
+          <t>MVF60NN152CMK50</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>NXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="inlineStr">
+        <is>
+          <t>MVTM36BF240M005A00</t>
+        </is>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>VICOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="13" t="inlineStr">
+        <is>
+          <t>MW6S004NT1</t>
+        </is>
+      </c>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>NXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="13" t="inlineStr">
+        <is>
+          <t>PI3301-00-LGIZ</t>
+        </is>
+      </c>
+      <c r="B72" s="13" t="inlineStr">
+        <is>
+          <t>VICOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="13" t="inlineStr">
+        <is>
+          <t>PI3302-00-LGIZ</t>
+        </is>
+      </c>
+      <c r="B73" s="13" t="inlineStr">
+        <is>
+          <t>VICOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="13" t="inlineStr">
+        <is>
+          <t>PVG612AS-TPBF</t>
+        </is>
+      </c>
+      <c r="B74" s="13" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="13" t="inlineStr">
+        <is>
+          <t>R5F5651EHDBG#20</t>
+        </is>
+      </c>
+      <c r="B75" s="13" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="13" t="inlineStr">
+        <is>
+          <t>R7FA4M1AB3CNB#BA0</t>
+        </is>
+      </c>
+      <c r="B76" s="13" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="13" t="inlineStr">
+        <is>
+          <t>S29GL032N90BFI032</t>
+        </is>
+      </c>
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t>SLB 9665TT2.0 FW5.63</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="13" t="inlineStr">
+        <is>
+          <t>SLB 9672VU2.0 FW15.23</t>
+        </is>
+      </c>
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t>SLB9665TT20FW563XUMA3</t>
+        </is>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="13" t="inlineStr">
+        <is>
+          <t>SLB9672VU20FW1523XTMA1</t>
+        </is>
+      </c>
+      <c r="B81" s="13" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="13" t="inlineStr">
+        <is>
+          <t>SMP1330-005LF</t>
+        </is>
+      </c>
+      <c r="B82" s="13" t="inlineStr">
+        <is>
+          <t>Skyworks</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="13" t="inlineStr">
+        <is>
+          <t>SMS7621-040LF</t>
+        </is>
+      </c>
+      <c r="B83" s="13" t="inlineStr">
+        <is>
+          <t>Skyworks</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="13" t="inlineStr">
+        <is>
+          <t>THS5010KJ</t>
+        </is>
+      </c>
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="13" t="inlineStr">
+        <is>
+          <t>TPS79133DBVR</t>
+        </is>
+      </c>
+      <c r="B85" s="13" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="13" t="inlineStr">
+        <is>
+          <t>V24C8M100BL</t>
+        </is>
+      </c>
+      <c r="B86" s="13" t="inlineStr">
+        <is>
+          <t>VICOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="16" t="inlineStr">
+        <is>
+          <t>V300B5T200BL</t>
+        </is>
+      </c>
+      <c r="B87" s="16" t="inlineStr">
+        <is>
+          <t>VICOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="13" t="inlineStr">
+        <is>
+          <t>ZMOD4410AI2R</t>
+        </is>
+      </c>
+      <c r="B88" s="13" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="13" t="inlineStr">
+        <is>
+          <t>ZMOD4410AI4R</t>
+        </is>
+      </c>
+      <c r="B89" s="13" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="13" t="inlineStr">
+        <is>
+          <t>ZMOD4510AI4R</t>
+        </is>
+      </c>
+      <c r="B90" s="13" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>14212R-500</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>深圳市福田区新亚洲电子市场雄盛电子商行</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>SOP-32</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>10+11+</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>￥500</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>3天内</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>100-500</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K1" s="29" t="n">
+        <v>45980.45726851852</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>14235R-2000</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>深圳市壹探网络技术有限公司</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>QFN-48</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>24+</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>￥176.99115</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>API实时</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1000(片)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K2" s="29" t="n">
+        <v>45980.46034722222</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>14235R-2000</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>深圳市楠兴电子有限公司</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>QFN48</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>22+</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>￥160</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1月内</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>100-500</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K3" s="29" t="n">
+        <v>45980.46034722222</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>14255R-100</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>深圳市壹探网络技术有限公司</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SMD/SMT</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>25+</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>￥41.293186</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>API实时</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2500(片)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K4" s="29" t="n">
+        <v>45980.46263888889</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FM25V02A-GTR</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>圣禾堂(深圳)电子科技有限公司</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SOIC-8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>25+</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>￥13.32</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1周内</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>100-500</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K5" s="29" t="n">
+        <v>45980.52131944444</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FM25V02A-GTR</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>深圳市华顺基业科技有限公司</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>25+</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>￥10</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1周内</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>100-500</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K6" s="29" t="n">
+        <v>45980.52130787037</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FM25V02A-GTR</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>深圳市瑞凯迪科技有限公司</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SOP8</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1607</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>￥7</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6天前</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4(片)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K7" s="29" t="n">
+        <v>45980.52130787037</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HS3002</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>深圳市永贝尔科技有限公司</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TQFP32</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>22+</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>￥0.68</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>3天内</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>&gt;10k</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K8" s="29" t="n">
+        <v>45980.52943287037</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>IR2110STRPBF</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>深圳市安美迪升科技有限公司</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SOP16</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>24+</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>￥3.3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1月内</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>&lt;50</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K9" s="29" t="n">
+        <v>45981.59938657407</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>IR2110STRPBF</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>深圳市志同创展电子有限公司</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SOIC-16</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>25+</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>￥3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1月内</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>&lt;50</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K10" s="29" t="n">
+        <v>45981.59938657407</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>IR2110STRPBF</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>深圳市森原科技电子有限公司</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SOP-16</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>24+</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>￥2.75</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1月内</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1K-5k</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K11" s="29" t="n">
+        <v>45981.59939814815</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>IR2110STRPBF</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>深圳煜思达电子有限公司</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SOP-16</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>22+</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>￥3</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1周内</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1K-5k</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K12" s="29" t="n">
+        <v>45981.59938657407</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>IRF5305PBF</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>深圳市安美迪升科技有限公司</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TO-220</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>25+</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>￥1.5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3天内</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>5k-10k</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K13" s="29" t="n">
+        <v>45980.54966435185</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>IRF540NPBF</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>深圳勤智芯电子有限公司</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TO-220</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>25+</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>全网最低</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3天内</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>&gt;10k</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K14" s="29" t="n">
+        <v>45981.62076388889</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>IRF540NPBF</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>深圳市佛信科技有限公司</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TO-220</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>25+</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>￥0.7</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1周内</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>50-100</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K15" s="29" t="n">
+        <v>45981.62077546296</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>IRF540NPBF</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>深圳市安美迪升科技有限公司</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TO-220</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>24+</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>￥0.695</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1月内</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>&gt;10k</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K16" s="29" t="n">
+        <v>45981.62078703703</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>IRF540NPBF</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>深圳市新大康科技有限公司</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TO-220</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>25+</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>￥0.72</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1月内</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>&gt;10k</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K17" s="29" t="n">
+        <v>45981.62079861111</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>IRF540NPBF</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>深圳市菱肯科技有限公司</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TO-220</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>22+</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>￥0.8</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>6天前</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2000(片)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K18" s="29" t="n">
+        <v>45981.62077546296</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>IRF640NPBF</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>深圳市新大康科技有限公司</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TO-220</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>24+25+</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>￥0.75</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>3天内</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>50-100</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K19" s="29" t="n">
+        <v>45981.61589120371</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>IRFZ44NPBF</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>深圳市新大康科技有限公司</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TO-220</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>24+</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>￥0.64</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1月内</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1K-5k</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K20" s="29" t="n">
+        <v>45981.63116898148</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>IRFZ44NPBF</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>深圳市森原科技电子有限公司</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TO-220</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>25+</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>￥0.6</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1月内</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>100-500</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K21" s="29" t="n">
+        <v>45981.63118055555</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>LTM4668AIY#PBF</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ADI</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>深圳京玺跃科技有限公司</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>BGA49</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>25+</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>￥55</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1月内</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>&lt;50</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K22" s="29" t="n">
+        <v>45980.45435185185</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MIMX8ML8CVNKZAB</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NXP</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>深圳时创天成科技有限公司(原北京时创天成)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LFBGA548</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>22+</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>￥170</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>3天内</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>&lt;50</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K23" s="29" t="n">
+        <v>45980.55940972222</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MPXM2202AS</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NXP</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>深圳市壹探网络技术有限公司</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>￥98.23</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>API实时</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>60起订</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K24" s="29" t="n">
+        <v>45980.56070601852</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MPXM2202AS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NXP</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>深圳市森浩伟业科技有限公司</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>MPAK-5</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>23+</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>￥88</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1月内</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>100-500</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K25" s="29" t="n">
+        <v>45980.56070601852</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MPXM2202AS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NXP</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>深圳舜鼎电子信息技术有限公司</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>SIP</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>23+</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>￥90</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1月内</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>100-500</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K26" s="29" t="n">
+        <v>45980.56071759259</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MVTM36BF240M005A00</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>VICOR</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>深圳市云科盛科技有限公司</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>MODULE</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>23+</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>￥2800</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1周内</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>100-500</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K27" s="29" t="n">
+        <v>45980.57714120371</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MW6S004NT1</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NXP</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>九州芯城电子商务(深圳)有限公司</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PLD-1.5</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>21+</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>￥200</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>3天内</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>100-500</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K28" s="29" t="n">
+        <v>45980.57878472222</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PVG612AS-TPBF</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>深圳市千喜电子实业有限公司</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>SMT6</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>25+</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>￥25</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1周内</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>100-500</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K29" s="29" t="n">
+        <v>45980.58863425926</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PVG612AS-TPBF</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>深圳煜思达电子有限公司</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SMT6</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>24+</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>￥23</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1月内</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>&lt;50</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K30" s="29" t="n">
+        <v>45980.58864583333</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SLB9665TT2.0FW5.63</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>深圳市光俊达科技有限公司</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TSSOP28</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>23+</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>￥25</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>3天内</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>500-1K</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K31" s="29" t="n">
+        <v>45980.6053125</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SMP1330-005LF</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Skyworks</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>深圳市艾赛芯科技有限公司</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SOT-23</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>25+</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>￥7</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1周内</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>100-500</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>TFL_ICStock1</t>
+        </is>
+      </c>
+      <c r="K32" s="29" t="n">
+        <v>45980.62015046296</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D90"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <cols>
+    <col width="36.83203125" customWidth="1" min="1" max="1"/>
+    <col width="37.6640625" customWidth="1" min="3" max="3"/>
+    <col width="44.1640625" customWidth="1" style="23" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16" customHeight="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>IRF540NPBF</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+      <c r="C1" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="D1" s="24" t="inlineStr">
+        <is>
+          <t>深圳市安美迪升科技有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>IRFZ44NPBF</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D2" s="23" t="inlineStr">
+        <is>
+          <t>深圳市森原科技电子有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HS3002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D3" s="23" t="inlineStr">
+        <is>
+          <t>深圳市永贝尔科技有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>IRF640NPBF</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>深圳市新大康科技有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>IRF5305PBF</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>深圳市安美迪升科技有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>IR2110STRPBF</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>深圳市森原科技电子有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FM25V02A-GTR</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>深圳市瑞凯迪科技有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SMP1330-005LF</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Skyworks</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>深圳市艾赛芯科技有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PVG612AS-TPBF</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>23</v>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>深圳煜思达电子有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>14255R-100</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>41.293186</v>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>深圳市壹探网络技术有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LTM4668AIY#PBF</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ADI</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>55</v>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>深圳京玺跃科技有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MPXM2202AS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NXP</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>88</v>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>深圳市森浩伟业科技有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>14235R-2000</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>160</v>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>深圳市楠兴电子有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MIMX8ML8CVNKZAB</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NXP</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>170</v>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>深圳时创天成科技有限公司(原北京时创天成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MW6S004NT1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NXP</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>200</v>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>九州芯城电子商务(深圳)有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>14212R-500</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>500</v>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>深圳市福田区新亚洲电子市场雄盛电子商行</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MVTM36BF240M005A00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>VICOR</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2800</v>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>深圳市云科盛科技有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TPS22810DRVR</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MT29F2G08ABAEAWP-IT:E</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MICRON</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ADSP-21489KSWZ-4B</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ADI</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DSPIC30F6014A-30I/PF</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MICROCHIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>IRLR8726TRPBF</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>IRPS5401MTRPBF</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CY7C68013A-56PVXC</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Infineon</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FF450R12ME4</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Infineon</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>IRS2004STRPBF</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>FF1400R12IP4</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Infineon</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>4202-004</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CTS (TUSONIX)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>4601-053</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CTS (TUSONIX)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CM1800HG-66X</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Mitsubishi</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>RM1200DG-66X</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mitsubishi</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TPS22810DRVR</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>11AA02E48T-I/TT</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MICROCHIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>14222R-800</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>15311R-1000</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>50020R-10</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>5-1879071-9</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>55010R-10</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>55040R-10</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>5P49V6901A000NLGI</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>72V211L15PFGI</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>8N3QV01FG-0055CDI8</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>APA150-PQG208I</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>MICROCHIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>AT25DF641A-MH-Y</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>AT45DB641E-SHN-T</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ATMEGA168-15AD</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>MICROCHIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CLA4603-085LF</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Skyworks</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>CLA4605-000</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Skyworks</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>CLA4605-085LF</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Skyworks</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CLA4606-085LF</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Skyworks</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>CLA4610-085LF</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Skyworks</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>CY62177EV18LL-70BAXI</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>CY7C2665KV18-450BZXI</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>CY7C68013A-56PVXC</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>CY7C68014A-56LTXC</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>DSPIC30F6014A-30I/PF</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>MICROCHIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>FS3000-1015</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>HS3101</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>HS4011</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>IPB072N15N3GATMA1</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>IPF016N06NF2S</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>IPL60R125P7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>IPT034N15NM6</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>IR2153STRPBF</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>IRF5210PBF</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>IRPS5401MTRPBF</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>IRS2004STRPBF</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>M41T94MH6F</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>STM</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>MRF101AN</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>NXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>MRF300AN</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>NXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>MRF300BN</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>NXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>MT29F512G08CMCEBJ4-37ITR:E</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>MICRON</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>MVF60NN152CMK50</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>NXP</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>PI3301-00-LGIZ</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>VICOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>PI3302-00-LGIZ</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>VICOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>R5F5651EHDBG#20</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>R7FA4M1AB3CNB#BA0</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>S29GL032N90BFI032</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SLB 9665TT2.0 FW5.63</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SLB 9672VU2.0 FW15.23</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>SLB9665TT20FW563XUMA3</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>SLB9672VU20FW1523XTMA1</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>INFINEON</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>SMS7621-040LF</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Skyworks</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>THS5010KJ</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>TPS79133DBVR</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>V24C8M100BL</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>VICOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>V300B5T200BL</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>VICOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>ZMOD4410AI2R</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>ZMOD4410AI4R</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ZMOD4510AI4R</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>RENESAS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
 </file>